--- a/2025/workspace/data.xlsx
+++ b/2025/workspace/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sahbab01/work/cca_fixtures/2025/workspace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BF91E7-38D3-C645-BF6E-DF04E0A2AE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027CDF1F-4105-B74A-8AF9-C55DC3DF06D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39980" yWindow="-25140" windowWidth="38400" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grounds" sheetId="1" r:id="rId1"/>
@@ -2733,11 +2733,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="5" max="5" width="48.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
     <col min="7" max="7" width="9.6640625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
@@ -3041,7 +3041,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>118</v>
       </c>
@@ -3151,28 +3151,28 @@
       <c r="L9" t="s">
         <v>425</v>
       </c>
-      <c r="N9" t="s">
-        <v>425</v>
-      </c>
-      <c r="P9" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="M9" t="s">
+        <v>425</v>
+      </c>
+      <c r="O9" t="s">
+        <v>425</v>
+      </c>
+      <c r="R9" t="s">
         <v>425</v>
       </c>
       <c r="S9" t="s">
         <v>425</v>
       </c>
-      <c r="T9" t="s">
-        <v>425</v>
-      </c>
       <c r="V9" t="s">
         <v>425</v>
       </c>
-      <c r="X9" t="s">
-        <v>425</v>
-      </c>
-      <c r="AA9" t="s">
+      <c r="Y9" t="s">
+        <v>425</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>425</v>
+      </c>
+      <c r="AB9" t="s">
         <v>425</v>
       </c>
       <c r="AC9" t="s">
@@ -3184,7 +3184,7 @@
         <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
         <v>186</v>
@@ -3445,7 +3445,7 @@
         <v>152</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="C19" t="s">
         <v>100</v>
@@ -3533,7 +3533,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>184</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>245</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C38" t="s">
         <v>135</v>
@@ -4940,7 +4940,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>288</v>
       </c>
@@ -5653,6 +5653,9 @@
       <c r="K84" t="s">
         <v>424</v>
       </c>
+      <c r="T84" t="s">
+        <v>425</v>
+      </c>
       <c r="AC84" t="s">
         <v>426</v>
       </c>
@@ -5949,9 +5952,6 @@
       <c r="F94" t="s">
         <v>408</v>
       </c>
-      <c r="I94" t="s">
-        <v>310</v>
-      </c>
       <c r="J94" t="s">
         <v>426</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>374</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>388</v>
       </c>
       <c r="B99" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="C99" t="s">
         <v>48</v>
@@ -6863,7 +6863,7 @@
         <v>62</v>
       </c>
       <c r="J117" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L117" t="s">
         <v>425</v>
@@ -7216,7 +7216,7 @@
         <v>83</v>
       </c>
       <c r="B127" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="C127" t="s">
         <v>154</v>
@@ -7348,7 +7348,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>83</v>
       </c>
@@ -7623,14 +7623,14 @@
   <autoFilter ref="A1:AC165" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Cam Kerala CC"/>
+        <filter val="Kimbolton CC"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:AC110">
       <sortCondition ref="F1:F165"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="AC107:AC136 J136:AB136 J137:AC175 J2:AC135">
+  <conditionalFormatting sqref="AC107:AC136 J136:AB136 J137:AC175 J2:AC8 J10:AC135 J9:M9 O9 R9:S9 V9:W9 AB9:AC9 Y9:Z9">
     <cfRule type="expression" dxfId="0" priority="12">
       <formula>#REF!</formula>
     </cfRule>
@@ -7690,7 +7690,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>AC107:AC136 J136:AB136 J137:AC175 J2:AC135</xm:sqref>
+          <xm:sqref>AC107:AC136 J136:AB136 J137:AC175 J2:AC8 J10:AC135 J9:M9 O9 R9:S9 V9:W9 AB9:AC9 Y9:Z9</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7700,7 +7700,7 @@
           <x14:formula1>
             <xm:f>constraints!$A$1:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:AC175</xm:sqref>
+          <xm:sqref>J2:AC8 J10:AC175 J9:M9 O9 R9:S9 V9:W9 Y9:Z9 AB9:AC9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
